--- a/www/BYD销售退货上传模板.xlsx
+++ b/www/BYD销售退货上传模板.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CSV_Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\棱星数据\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98DC8567-9AE7-4846-9373-F573A7A442D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05F1E68-6B47-4189-8865-83AE507676C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
   <si>
     <t>DFCDD0802</t>
   </si>
@@ -82,92 +82,87 @@
     <t>-34.80 CNY</t>
   </si>
   <si>
+    <t>单据编号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>销售组织编码</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>销售组织名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>状态（抬头）（客户）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成状态（抬头）（客户退货）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>销售订单编号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>要求日期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>客户编码</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>客户名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>卖方编码</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>卖方名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>退货原因编码</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>退货原因名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>员工编码</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>员工名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>行号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>物料编码</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>物料名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>退货数量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>退货净值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>月/日历年</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>单据编号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>销售组织编码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>销售组织名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>状态（抬头）（客户）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>完成状态（抬头）（客户退货）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>销售订单编号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>要求日期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>客户编码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>客户名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>卖方编码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>卖方名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>退货原因编码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>退货原因名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>员工编码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>员工名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>行号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>物料编码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>物料名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>退货数量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>退货净值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -175,7 +170,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -225,10 +220,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -532,7 +527,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.6640625" style="3" bestFit="1" customWidth="1"/>
@@ -545,67 +540,67 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
@@ -736,11 +731,6 @@
       </c>
       <c r="U3" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="S16" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -757,7 +747,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5385A6AD-2AB0-434B-8611-F267C86D58A1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C95FA402-733C-43CA-903D-C2C91773751E}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>